--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C179"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3484,6 +3484,108 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>10月9日</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>王森飞</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>客情走访，用户不在家，未交谈，换个时间点再访</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10月9日</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>朱肖水</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>客情走访，用户不在家，未交谈，换个时间点再访</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10月9日</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>潘如军</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>客情走访，用户不在家，未交谈，再约时间回访</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10月9日</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>施君华</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>客情走访：用料已更换，现小料用唐人神、大料用天翔819（挂账价114，属低档料）；此前用添祥、海大料，跟添祥、郑海杰拿料，现跟谁拿料待问清；鱼现八两左右，预计11月初出鱼；出鱼后回访核实天翔819这造包产</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>10月9日</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>郑康强</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>拜访：跟田永均拿料，田永均不拉通威，用户也没法拉；本人之前用过通威但用得少；现用祥泰（田永均供货）；聊天意愿低</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>10月9日</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>朱耀武</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>拜访：用户不愿意交谈，结束</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3586,6 +3586,23 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>陈浩成</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>测水补录：用户两口塘（塘号按测水时间标序——14:20塘、14:23塘）现场测水，pH均7.4，亚硝酸盐0.15/0.10（均低于0.28预警线、水质正常、未标预警），氨氮因检测试剂用完未测、待补；该用户为今日新增走访对象，暂无其他养殖近况，后续跟进补建摸牌表与档案、并确认塘口具体位置。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3603,6 +3603,74 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>丁志开</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>客情走访：基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威，但经销商马津深不给拉；准备拿苗原13号推16号；其弟丁开福苗塘放60万苗，趁早刺激快速转料用开口乐；5口塘亚盐偏高已推降亚盐动保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>宋平</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>客情走访：七口塘，计划装料塔、对通威认可度高；主用海大2552偶混渝泰/粤海，跟周公宝拿料；老婆湖南人；主动问价，转化机会明确；与唐行平（湖南老乡）互相认识可交叉跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>陈南高</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>客情走访（聊天获知+直接走访）：百洋直供用户，从厂里直拿料不经经销商，用百洋最低端料、包产不高、转料意愿不强；其租塘明年5月到期，届时另找养户租塘续养、不找经销商（找经销商租就被绑定拿料更贵）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>陈浩成</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>15:07客情走访（新增用户）：公司饲料活动拿料，8月即参加活动拉通威；本兆前段用一点翔泰后转通威，下一兆提了一嘴要用全程通威；加强拜访频次、做好客情服务。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3671,6 +3671,23 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>唐行平</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>出鱼期抓鱼中，未拜访、未交谈，择日再访；待出鱼后回访补建档案。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>出鱼期抓鱼中，未拜访、未交谈，择日再访；待出鱼后回访补建档案。</t>
+          <t>【养殖关键节点】出鱼/抓鱼：2026-10-10（出鱼期抓鱼中）；放苗时间：待回访补全。出鱼期未拜访、未交谈，择日再访；待出鱼后回访补建档案与养殖周期信息。</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C191"/>
+  <dimension ref="A1:C192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3688,6 +3688,23 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>丁开福</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>【养殖关键节点】放苗：新抓60万尾苗放入，平均4800尾/斤（约125斤）；与丁志开拿苗节点（16号）同期，借放苗刺激丁志开快速转料、推通威开口乐。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -3691,7 +3691,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>10月10日</t>
+          <t>9月16日</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>【养殖关键节点】放苗：新抓60万尾苗放入，平均4800尾/斤（约125斤）；与丁志开拿苗节点（16号）同期，借放苗刺激丁志开快速转料、推通威开口乐。</t>
+          <t>【养殖关键节点】放苗（9月16日）：新抓60万尾苗放入，平均4800尾/斤（约125斤）；借放苗刺激兄长丁志开快速转料、推通威开口乐（丁志开本人拿苗节点为10月16号，二者非同期）。</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C192"/>
+  <dimension ref="A1:C193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3705,6 +3705,23 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>黄少雄</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>新补录用户（陈南高聊天获悉，同音'黄绍雄'电话13036004961）；现用翔泰料、包产稳定且高，陈南高亲述高产样板/转介绍突破点。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户拜访记录汇总.xlsx
+++ b/数据/养殖客户拜访记录汇总.xlsx
@@ -3713,12 +3713,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>黄少雄</t>
+          <t>黄绍雄</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>新补录用户（陈南高聊天获悉，同音'黄绍雄'电话13036004961）；现用翔泰料、包产稳定且高，陈南高亲述高产样板/转介绍突破点。</t>
+          <t>新补录用户（陈南高聊天获悉，电话13036004961）；现用翔泰料、包产稳定且高，陈南高亲述高产样板/转介绍突破点。</t>
         </is>
       </c>
     </row>
